--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122571141</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tyftingemar, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>593221</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6395451</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122571141</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122571141</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122571141</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122571141</v>
       </c>
       <c r="B3" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122571141</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>90960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122571141</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 59231-2022 artfynd.xlsx
+++ b/artfynd/A 59231-2022 artfynd.xlsx
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105938814</v>
+        <v>122571141</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 59231, Dagsbo, Sm</t>
+          <t>Tyftingemar, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593269.2249252535</v>
+        <v>593221</v>
       </c>
       <c r="R2" t="n">
-        <v>6395443.478257386</v>
+        <v>6395451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,61 +784,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122571141</v>
+        <v>105938814</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tyftingemar, Sm</t>
+          <t>A 59231, Dagsbo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593221</v>
+        <v>593269</v>
       </c>
       <c r="R3" t="n">
-        <v>6395451</v>
+        <v>6395443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
